--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,300 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120463436</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Perstorpastugan knärot 500 m sv, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>571292</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6543272</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D-Kat-0638</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Området anmält för slutavverkning</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Adoxa Janne Elmhag</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120463575</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108811</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Perstorpastugan svinrot 450 m sv, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571433</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6543263</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D-Kat-0639</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vid sidan av skogsvägen. Området är anmält för slutavverkning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogsvägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Adoxa Janne Elmhag</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Adoxa Janne Elmhag</t>
+          <t>Adoxa Janne Elmhag, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120463436</v>
+        <v>120463575</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -855,14 +855,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Perstorpastugan knärot 500 m sv, Srm</t>
+          <t>Perstorpastugan svinrot 450 m sv, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571292</v>
+        <v>571433</v>
       </c>
       <c r="R3" t="n">
-        <v>6543272</v>
+        <v>6543263</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>D-Kat-0638</t>
+          <t>D-Kat-0639</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Området anmält för slutavverkning</t>
+          <t>vid sidan av skogsvägen. Området är anmält för slutavverkning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>skogsvägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120463575</v>
+        <v>120463436</v>
       </c>
       <c r="B4" t="n">
-        <v>108811</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,35 +958,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Perstorpastugan svinrot 450 m sv, Srm</t>
+          <t>Perstorpastugan knärot 500 m sv, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571433</v>
+        <v>571292</v>
       </c>
       <c r="R4" t="n">
-        <v>6543263</v>
+        <v>6543272</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>D-Kat-0639</t>
+          <t>D-Kat-0638</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>vid sidan av skogsvägen. Området är anmält för slutavverkning</t>
+          <t>Området anmält för slutavverkning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>skogsvägkant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Adoxa Janne Elmhag, Bo Karlsson</t>
+          <t>Bo Karlsson, Adoxa Janne Elmhag</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120463575</v>
+        <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -855,14 +855,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Perstorpastugan svinrot 450 m sv, Srm</t>
+          <t>Perstorpastugan knärot 500 m sv, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571433</v>
+        <v>571292</v>
       </c>
       <c r="R3" t="n">
-        <v>6543263</v>
+        <v>6543272</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>D-Kat-0639</t>
+          <t>D-Kat-0638</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vid sidan av skogsvägen. Området är anmält för slutavverkning</t>
+          <t>Området anmält för slutavverkning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>skogsvägkant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120463436</v>
+        <v>120463575</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>108811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,35 +958,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Perstorpastugan knärot 500 m sv, Srm</t>
+          <t>Perstorpastugan svinrot 450 m sv, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571292</v>
+        <v>571433</v>
       </c>
       <c r="R4" t="n">
-        <v>6543272</v>
+        <v>6543263</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>D-Kat-0638</t>
+          <t>D-Kat-0639</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Området anmält för slutavverkning</t>
+          <t>vid sidan av skogsvägen. Området är anmält för slutavverkning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>skogsvägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>120463436</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,120 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122401381</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>jaktstugan, Flundern, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571472</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543184</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Lundell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Lundell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28561-2024 artfynd.xlsx
+++ b/artfynd/A 28561-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,120 +1091,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>122401381</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>jaktstugan, Flundern, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>571472</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6543184</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Katrineholm</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Floda</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Thomas Lundell</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Thomas Lundell</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
